--- a/AAAGameData/DataTables/MakeupTask.xlsx
+++ b/AAAGameData/DataTables/MakeupTask.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27000" windowHeight="17175"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
   <si>
     <t>#</t>
   </si>
@@ -52,6 +52,9 @@
     <t>Reward</t>
   </si>
   <si>
+    <t>Rate</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -68,6 +71,9 @@
   </si>
   <si>
     <t>奖励值</t>
+  </si>
+  <si>
+    <t>倍率</t>
   </si>
 </sst>
 </file>
@@ -1277,22 +1283,28 @@
       <c r="F2" t="s">
         <v>5</v>
       </c>
+      <c r="G2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="G3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:8">
@@ -1300,18 +1312,20 @@
         <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="H4" s="1"/>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:8">
@@ -1328,7 +1342,9 @@
       <c r="F5" s="4">
         <v>0.3</v>
       </c>
-      <c r="G5" s="4"/>
+      <c r="G5" s="4">
+        <v>1</v>
+      </c>
       <c r="H5" s="4"/>
     </row>
     <row r="6" customHeight="1" spans="1:8">
@@ -1345,7 +1361,9 @@
       <c r="F6" s="4">
         <v>0.4</v>
       </c>
-      <c r="G6" s="4"/>
+      <c r="G6" s="4">
+        <v>1</v>
+      </c>
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8">
@@ -1362,7 +1380,9 @@
       <c r="F7" s="4">
         <v>0.5</v>
       </c>
-      <c r="G7" s="4"/>
+      <c r="G7" s="4">
+        <v>1</v>
+      </c>
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8">
@@ -1379,7 +1399,9 @@
       <c r="F8" s="4">
         <v>10</v>
       </c>
-      <c r="G8" s="4"/>
+      <c r="G8" s="4">
+        <v>1</v>
+      </c>
       <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:8">
@@ -1396,6 +1418,9 @@
       <c r="F9" s="4">
         <v>100</v>
       </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:8">
       <c r="B10">
@@ -1410,12 +1435,14 @@
       <c r="F10" s="4">
         <v>0</v>
       </c>
-      <c r="G10" s="4"/>
+      <c r="G10" s="4">
+        <v>1</v>
+      </c>
       <c r="H10" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="E1:F1 G1:AA1">
+    <dataValidation type="list" allowBlank="1" sqref="E1:AA1">
       <formula1>"i18n"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="I3:AA3">

--- a/AAAGameData/DataTables/MakeupTask.xlsx
+++ b/AAAGameData/DataTables/MakeupTask.xlsx
@@ -49,7 +49,7 @@
     <t>Mon</t>
   </si>
   <si>
-    <t>Reward</t>
+    <t>Pcard</t>
   </si>
   <si>
     <t>Rate</t>

--- a/AAAGameData/DataTables/MakeupTask.xlsx
+++ b/AAAGameData/DataTables/MakeupTask.xlsx
@@ -1248,7 +1248,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="23.8571428571429" customWidth="1"/>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="3">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="E5" s="4">
         <v>0</v>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="3">
-        <v>8</v>
+        <v>150</v>
       </c>
       <c r="E6" s="4">
         <v>0</v>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="3">
-        <v>18</v>
+        <v>200</v>
       </c>
       <c r="E7" s="4">
         <v>0</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="3">
-        <v>30</v>
+        <v>400</v>
       </c>
       <c r="E8" s="4">
         <v>0</v>
@@ -1406,39 +1406,21 @@
     </row>
     <row r="9" spans="1:8">
       <c r="B9">
-        <v>5</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9">
-        <v>40</v>
+        <v>6</v>
+      </c>
+      <c r="D9" s="3">
+        <v>600</v>
       </c>
       <c r="E9" s="4">
+        <v>10000</v>
+      </c>
+      <c r="F9" s="4">
         <v>0</v>
       </c>
-      <c r="F9" s="4">
-        <v>100</v>
-      </c>
-      <c r="G9">
+      <c r="G9" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="B10">
-        <v>6</v>
-      </c>
-      <c r="D10" s="3">
-        <v>50</v>
-      </c>
-      <c r="E10" s="4">
-        <v>10000</v>
-      </c>
-      <c r="F10" s="4">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4">
-        <v>1</v>
-      </c>
-      <c r="H10" s="4"/>
+      <c r="H9" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="2">
